--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Hardware/Analisis Eléctrico y Térmico/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BF010325F10992A21E5D2AAF911A502F96B28E63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1438F95-4E96-4A5B-83B8-A584B48BD07F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
@@ -17,18 +18,28 @@
     <sheet name="PCB2.Sensores" sheetId="3" r:id="rId3"/>
     <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>TOTAL</t>
   </si>
@@ -453,13 +464,50 @@
       </rPr>
       <t>= 3V</t>
     </r>
+  </si>
+  <si>
+    <t>ICE40HX4K-TQ144</t>
+  </si>
+  <si>
+    <t>1N4448HSW-7-F </t>
+  </si>
+  <si>
+    <t>IS25LP032D-JNLE </t>
+  </si>
+  <si>
+    <t>MCP1725-ADJ E/SN </t>
+  </si>
+  <si>
+    <t>IL = 0 mA, VIN =  VIN ≥ 2.3V and 
+VIN ≥ VOUT(MAX) + VDROPOUT(MAX), VOUT = 0.8V to 5.0V</t>
+  </si>
+  <si>
+    <t>M20-6102045 </t>
+  </si>
+  <si>
+    <t>CON-SIL2</t>
+  </si>
+  <si>
+    <t>MCSJK-3N-16.00-3.3-50-B </t>
+  </si>
+  <si>
+    <t>HSMS-C170</t>
+  </si>
+  <si>
+    <t>L77HDE15SD1CH4F</t>
+  </si>
+  <si>
+    <t>Quiescent current</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,6 +550,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -523,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -554,9 +614,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -836,7 +895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1036,8 +1095,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -1104,7 +1163,112 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E12" si="0">C4*D4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>3.3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1113,7 +1277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1282,7 +1446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1354,37 +1518,35 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2">
-        <v>70</v>
-      </c>
-      <c r="E4" s="2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4">
+        <v>3.3</v>
+      </c>
+      <c r="D4">
+        <f>70*10^(-6)</f>
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="E4">
+        <f>C4*D4</f>
+        <v>2.3099999999999998E-4</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>SUM(E4:E5)</f>
+        <v>2.3099999999999998E-4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Hardware/Analisis Eléctrico y Térmico/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BF010325F10992A21E5D2AAF911A502F96B28E63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1438F95-4E96-4A5B-83B8-A584B48BD07F}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="11_BF010325F10992A21E5D2AAF911A502F96B28E63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B9D9C8-5466-4B1D-9449-86D2C61CD9F1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
   <si>
     <t>TOTAL</t>
   </si>
@@ -182,12 +182,6 @@
       </rPr>
       <t xml:space="preserve"> = 0.8V to 5.0V </t>
     </r>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>3.3</t>
   </si>
   <si>
     <t>Does not include current through the pull-up resistor on USBDP In USB suspend mode, the D+ voltage can go up to a maximum of 3.8 V.</t>
@@ -271,9 +265,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">100 000 </t>
-  </si>
-  <si>
     <t>TEL0132 </t>
   </si>
   <si>
@@ -302,9 +293,6 @@
   </si>
   <si>
     <t xml:space="preserve">Per supply pin </t>
-  </si>
-  <si>
-    <t>0.55</t>
   </si>
   <si>
     <r>
@@ -438,9 +426,6 @@
     <t>LAMBDA62-8D</t>
   </si>
   <si>
-    <t>39.6</t>
-  </si>
-  <si>
     <r>
       <t>25°C, V</t>
     </r>
@@ -478,10 +463,6 @@
     <t>MCP1725-ADJ E/SN </t>
   </si>
   <si>
-    <t>IL = 0 mA, VIN =  VIN ≥ 2.3V and 
-VIN ≥ VOUT(MAX) + VDROPOUT(MAX), VOUT = 0.8V to 5.0V</t>
-  </si>
-  <si>
     <t>M20-6102045 </t>
   </si>
   <si>
@@ -501,6 +482,52 @@
   </si>
   <si>
     <t>W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">power </t>
+  </si>
+  <si>
+    <t>P_3,3V</t>
+  </si>
+  <si>
+    <t>P_1,2V</t>
+  </si>
+  <si>
+    <t>mW</t>
+  </si>
+  <si>
+    <t>standby power</t>
+  </si>
+  <si>
+    <t>FRD Quad at 133MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IL = 0 mA, VIN = Note 1,
+VOUT = 0.8V to 5.0V</t>
+  </si>
+  <si>
+    <t>Supply Current</t>
+  </si>
+  <si>
+    <t>P_2,6V</t>
+  </si>
+  <si>
+    <t>MMBT3904-7-F</t>
+  </si>
+  <si>
+    <t>NDS332P</t>
+  </si>
+  <si>
+    <t>S6BZRSM4ATFLFSN</t>
+  </si>
+  <si>
+    <t>M20-6102045</t>
+  </si>
+  <si>
+    <t>ZHR-6</t>
+  </si>
+  <si>
+    <t>P_5V</t>
   </si>
 </sst>
 </file>
@@ -583,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -616,6 +643,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,6 +661,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -896,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -988,104 +1022,152 @@
         <v>1500</v>
       </c>
       <c r="E4">
-        <v>7500</v>
+        <f>C4*D4*(10^(-6))</f>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="5" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>220</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E9" si="0">C5*D5*(10^(-6))</f>
+        <v>1.0999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D7" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>8.9999999999999992E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D8">
-        <v>18</v>
-      </c>
+      <c r="C7" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="1"/>
       <c r="E8">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E9">
+        <f>C9*D9*(10^(-6))</f>
+        <v>0.32999999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="1">
+        <f>SUMIFS(E$4:E$14,C$4:C$14,"5")</f>
+        <v>8.6899999999999998E-3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" ref="D16:D17" si="1">SUMIFS(E$4:E$14,C$4:C$14,"3,3")</f>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
         <v>21</v>
       </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11">
-        <v>330000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D14" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="G18" t="s">
-        <v>23</v>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="1">
+        <f>SUMIFS(E$4:E$14,C$4:C$14,"2,6")</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <f>SUM(D15:D17)</f>
+        <v>0.33868999999999994</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="1">
+        <f>D19*1000</f>
+        <v>338.68999999999994</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1096,10 +1178,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
@@ -1164,76 +1246,105 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E12" si="0">C4*D4</f>
-        <v>0</v>
+        <f>C4*D4</f>
+        <v>6.929999999999999E-5</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>42</v>
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
       </c>
       <c r="C5">
         <v>3.3</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C5*D5</f>
+        <v>6.929999999999999E-5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>43</v>
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>3.3</v>
+      </c>
+      <c r="D6">
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>45</v>
+        <f>C6*D6</f>
+        <v>6.929999999999999E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7">
+        <v>3.3</v>
+      </c>
+      <c r="D7">
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C7*D7</f>
+        <v>6.929999999999999E-5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="E8:E16" si="0">C8*D8</f>
+        <v>2.5199999999999999E-5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>47</v>
+      <c r="A9" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1245,29 +1356,177 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10">
+        <v>3.3</v>
+      </c>
+      <c r="D10">
+        <f>17*10^(-3)</f>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>49</v>
+        <v>5.6100000000000004E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11">
+        <v>3.3</v>
+      </c>
+      <c r="D11">
+        <f>220*10^(-6)</f>
+        <v>2.1999999999999998E-4</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.2599999999999987E-4</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>50</v>
+      <c r="A12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14">
+        <v>3.3</v>
+      </c>
+      <c r="D14">
+        <f>15*10^(-3)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>4.9499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>2.6</v>
+      </c>
+      <c r="D15">
+        <f>20*10^(-3)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>5.2000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
+        <v>0.1066032</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <f>SUM(C19:C21)</f>
+        <v>0.1586284</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="1">
+        <f>C23*1000</f>
+        <v>158.6284</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1278,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1323,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1350,94 +1609,243 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
+      <c r="C4" s="2">
+        <v>3.3</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>330</v>
+        <f>(C4*D4)/1000</f>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
+      <c r="C5" s="2">
+        <v>3.3</v>
       </c>
       <c r="D5">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
+      <c r="E5">
+        <f t="shared" ref="E5:E15" si="0">(C5*D5)/1000</f>
+        <v>3.9599999999999996E-2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3.3</v>
       </c>
       <c r="D6">
         <v>240</v>
       </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0.79200000000000004</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2"/>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
+      <c r="D9" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="2"/>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
       <c r="C12" s="2"/>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
+        <v>1.1616</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"5,0")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <f>SUM(D18:D20)</f>
+        <v>1.1616</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D23" s="1">
+        <f>D22*1000</f>
+        <v>1161.5999999999999</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1519,10 +1927,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>3.3</v>
@@ -1536,23 +1944,41 @@
         <v>2.3099999999999998E-4</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1">
+        <f>E4</f>
+        <v>2.3099999999999998E-4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <f>SUM(E4:E5)</f>
         <v>2.3099999999999998E-4</v>
       </c>
-      <c r="F7" t="s">
-        <v>52</v>
+      <c r="F7" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16">
+        <f>E7*1000</f>
+        <v>0.23099999999999998</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Hardware/Analisis Eléctrico y Térmico/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Invitado(pass user)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="11_BF010325F10992A21E5D2AAF911A502F96B28E63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B9D9C8-5466-4B1D-9449-86D2C61CD9F1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="PCB2.Sensores" sheetId="3" r:id="rId3"/>
     <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
   <si>
     <t>TOTAL</t>
   </si>
@@ -220,51 +219,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>USB 2.0 FS, UART at 1-Mbps single channel, no GPIO switching at V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">CC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>= 5 V, V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CCIO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 5 V</t>
-    </r>
-  </si>
-  <si>
     <t>TEL0132 </t>
   </si>
   <si>
@@ -284,9 +238,6 @@
   </si>
   <si>
     <t>XC9141B50DMR-G </t>
-  </si>
-  <si>
-    <t>LQH5BPN4R7NT0L </t>
   </si>
   <si>
     <t>Currents (mA)</t>
@@ -512,29 +463,84 @@
     <t>P_2,6V</t>
   </si>
   <si>
-    <t>MMBT3904-7-F</t>
-  </si>
-  <si>
-    <t>NDS332P</t>
-  </si>
-  <si>
-    <t>S6BZRSM4ATFLFSN</t>
-  </si>
-  <si>
-    <t>M20-6102045</t>
-  </si>
-  <si>
-    <t>ZHR-6</t>
-  </si>
-  <si>
     <t>P_5V</t>
+  </si>
+  <si>
+    <r>
+      <t>USB 2.0 FS, UART at 1-Mbps single channel, no GPIO switching at V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= 5 V,       V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CCIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 5 V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <t>P_3,7V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,12 +586,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -642,8 +642,10 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -929,15 +931,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="20.140625" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
@@ -1041,7 +1043,7 @@
         <v>220</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E9" si="0">C5*D5*(10^(-6))</f>
+        <f t="shared" ref="E5:E7" si="0">C5*D5*(10^(-6))</f>
         <v>1.0999999999999998E-3</v>
       </c>
     </row>
@@ -1050,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -1063,7 +1065,7 @@
         <v>8.9999999999999992E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="8" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="11" t="s">
         <v>20</v>
@@ -1077,97 +1079,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="1"/>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100000</v>
+      </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C8*D8*(10^(-6))</f>
+        <v>0.32999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>100000</v>
+        <v>3.7</v>
+      </c>
+      <c r="D9">
+        <v>5000000</v>
       </c>
       <c r="E9">
-        <f>C9*D9*(10^(-6))</f>
-        <v>0.32999999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D12" s="1"/>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"5")</f>
+        <v>8.6899999999999998E-3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1">
-        <f>SUMIFS(E$4:E$14,C$4:C$14,"5")</f>
-        <v>8.6899999999999998E-3</v>
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
+        <v>0.32999999999999996</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:D17" si="1">SUMIFS(E$4:E$14,C$4:C$14,"3,3")</f>
-        <v>0.32999999999999996</v>
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <f>SUM(D14:D17)</f>
+        <v>18.83869</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="1">
+        <f>D18*1000</f>
+        <v>18838.689999999999</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="1">
-        <f>SUMIFS(E$4:E$14,C$4:C$14,"2,6")</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <f>SUM(D15:D17)</f>
-        <v>0.33868999999999994</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="1">
-        <f>D19*1000</f>
-        <v>338.68999999999994</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1177,7 +1197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1246,10 +1266,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.3</v>
@@ -1265,10 +1285,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>3.3</v>
@@ -1284,10 +1304,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>3.3</v>
@@ -1303,10 +1323,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>3.3</v>
@@ -1322,10 +1342,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>1.2</v>
@@ -1341,7 +1361,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>3.3</v>
@@ -1356,10 +1376,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>3.3</v>
@@ -1375,10 +1395,10 @@
     </row>
     <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>3.3</v>
@@ -1394,7 +1414,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1409,7 +1429,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1424,10 +1444,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>3.3</v>
@@ -1443,7 +1463,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>2.6</v>
@@ -1459,7 +1479,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1474,38 +1494,38 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
         <v>0.1066032</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
         <v>2.5199999999999999E-5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
         <v>5.2000000000000005E-2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -1517,7 +1537,7 @@
         <v>0.1586284</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -1526,7 +1546,7 @@
         <v>158.6284</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1536,8 +1556,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1582,7 +1602,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1609,7 +1629,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="2">
@@ -1625,7 +1645,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="2">
@@ -1635,16 +1655,16 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E15" si="0">(C5*D5)/1000</f>
+        <f t="shared" ref="E5:E10" si="0">(C5*D5)/1000</f>
         <v>3.9599999999999996E-2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2">
         <v>3.3</v>
@@ -1659,193 +1679,158 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="16">
         <v>5</v>
       </c>
-      <c r="E8">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.3</v>
+      </c>
       <c r="D9" s="2">
         <v>0.55000000000000004</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.815E-3</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>3.3</v>
       </c>
+      <c r="D10">
+        <v>800</v>
+      </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="2"/>
-      <c r="E11">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUMIFS(E$4:E$11,C$4:C$11,"3,3")</f>
+        <v>3.8034150000000002</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1">
+        <f>SUMIFS(E$4:E$11,C$4:C$11,"5,0")</f>
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="1">
+        <f>SUMIFS(E$4:E$11,C$4:C$11,"2,6")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="E12">
-        <f t="shared" si="0"/>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>60</v>
+      <c r="D17" s="1">
+        <f>SUM(D13:D15)</f>
+        <v>3.9034150000000003</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1">
+        <f>D17*1000</f>
+        <v>3903.4150000000004</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
-        <v>1.1616</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"5,0")</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <f>SUM(D18:D20)</f>
-        <v>1.1616</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="1">
-        <f>D22*1000</f>
-        <v>1161.5999999999999</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1854,7 +1839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1926,13 +1911,13 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>34</v>
+      <c r="A4" t="s">
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4">
+        <v>43</v>
+      </c>
+      <c r="C4" s="3">
         <v>3.3</v>
       </c>
       <c r="D4">
@@ -1946,14 +1931,14 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1">
         <f>E4</f>
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1965,19 +1950,19 @@
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15">
         <f>E7*1000</f>
         <v>0.23099999999999998</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
   <si>
     <t>TOTAL</t>
   </si>
@@ -181,9 +181,6 @@
       </rPr>
       <t xml:space="preserve"> = 0.8V to 5.0V </t>
     </r>
-  </si>
-  <si>
-    <t>Does not include current through the pull-up resistor on USBDP In USB suspend mode, the D+ voltage can go up to a maximum of 3.8 V.</t>
   </si>
   <si>
     <r>
@@ -534,6 +531,15 @@
   </si>
   <si>
     <t>P_3,7V</t>
+  </si>
+  <si>
+    <t>4-Layer JC51-7 Standard Board, Natural Convection</t>
+  </si>
+  <si>
+    <t>Theta_jar(Cº/W)</t>
+  </si>
+  <si>
+    <t>(?)(?)</t>
   </si>
 </sst>
 </file>
@@ -610,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -647,6 +653,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -942,15 +951,15 @@
     <col min="5" max="5" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="20.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.42578125" customWidth="1"/>
     <col min="14" max="14" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -964,7 +973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -972,7 +981,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1004,13 +1013,13 @@
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1028,63 +1037,114 @@
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="str">
+        <f>B4</f>
+        <v xml:space="preserve">Charging </v>
+      </c>
+      <c r="K4">
+        <f>E4</f>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="M4">
+        <v>230</v>
+      </c>
+      <c r="N4">
+        <f>K4*M4</f>
+        <v>1.7249999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="J5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N9" si="0">K5*M5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>220</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E7" si="0">C5*D5*(10^(-6))</f>
-        <v>1.0999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
       <c r="D6">
+        <v>220</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E7" si="1">C6*D6*(10^(-6))</f>
+        <v>1.0999999999999998E-3</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="7" t="str">
+        <f>B6</f>
+        <v xml:space="preserve">IL = 0 mA, VIN = Note 1             VOUT = 0.8V to 5.0V </v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:K9" si="2">E6</f>
+        <v>1.0999999999999998E-3</v>
+      </c>
+      <c r="M6">
+        <v>163</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0.17929999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>8.9999999999999992E-5</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="7" t="str">
+        <f t="shared" ref="J7:J8" si="3">B7</f>
+        <v>USB 2.0 FS, UART at 1-Mbps single channel, no GPIO switching at VCC = 5 V,       VCCIO = 5 V</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>8.9999999999999992E-5</v>
+      </c>
+      <c r="M7">
+        <v>62</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="0"/>
-        <v>8.9999999999999992E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="8" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="D7"/>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5.5799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2">
         <v>3.3</v>
@@ -1096,8 +1156,32 @@
         <f>C8*D8*(10^(-6))</f>
         <v>0.32999999999999996</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Per supply pin </v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="M8" s="8">
+        <v>115.2</v>
+      </c>
+      <c r="N8">
+        <f>K8*M8</f>
+        <v>38.015999999999998</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1108,60 +1192,76 @@
         <v>5000000</v>
       </c>
       <c r="E9">
+        <f>C9*D9*(10^(-6))</f>
         <v>18.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <f t="shared" si="2"/>
+        <v>18.5</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"5")</f>
         <v>8.6899999999999998E-3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1">
         <v>18.5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1173,7 +1273,7 @@
         <v>18.83869</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1182,12 +1282,12 @@
         <v>18838.689999999999</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1204,6 +1304,7 @@
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1266,10 +1367,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>3.3</v>
@@ -1282,13 +1383,25 @@
         <f>C4*D4</f>
         <v>6.929999999999999E-5</v>
       </c>
+      <c r="I4" t="str">
+        <f>A4</f>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J4" t="str">
+        <f>B4</f>
+        <v>standby power</v>
+      </c>
+      <c r="K4">
+        <f>E4</f>
+        <v>6.929999999999999E-5</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>3.3</v>
@@ -1301,13 +1414,25 @@
         <f>C5*D5</f>
         <v>6.929999999999999E-5</v>
       </c>
+      <c r="I5" t="str">
+        <f t="shared" ref="I5:I16" si="0">A5</f>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" ref="J5:J14" si="1">B5</f>
+        <v>standby power</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K16" si="2">E5</f>
+        <v>6.929999999999999E-5</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>3.3</v>
@@ -1320,13 +1445,25 @@
         <f>C6*D6</f>
         <v>6.929999999999999E-5</v>
       </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="1"/>
+        <v>standby power</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>6.929999999999999E-5</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>3.3</v>
@@ -1339,13 +1476,25 @@
         <f>C7*D7</f>
         <v>6.929999999999999E-5</v>
       </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>standby power</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>6.929999999999999E-5</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>1.2</v>
@@ -1355,13 +1504,25 @@
         <v>2.0999999999999999E-5</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:E16" si="0">C8*D8</f>
+        <f t="shared" ref="E8:E16" si="3">C8*D8</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">power </v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
         <v>2.5199999999999999E-5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>3.3</v>
@@ -1370,16 +1531,24 @@
         <v>0</v>
       </c>
       <c r="E9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
         <f t="shared" si="0"/>
+        <v>1N4448HSW-7-F </v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>3.3</v>
@@ -1389,16 +1558,28 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="E10">
+        <f t="shared" si="3"/>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="I10" t="str">
         <f t="shared" si="0"/>
+        <v>IS25LP032D-JNLE </v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>FRD Quad at 133MHz</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
         <v>5.6100000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>3.3</v>
@@ -1408,13 +1589,26 @@
         <v>2.1999999999999998E-4</v>
       </c>
       <c r="E11">
+        <f t="shared" si="3"/>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="0"/>
+        <v>MCP1725-ADJ E/SN </v>
+      </c>
+      <c r="J11" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
+VOUT = 0.8V to 5.0V</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
         <v>7.2599999999999987E-4</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1423,13 +1617,24 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>M20-6102045 </v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1438,16 +1643,27 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>CON-SIL2</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>3.3</v>
@@ -1457,13 +1673,25 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E14">
+        <f t="shared" si="3"/>
+        <v>4.9499999999999995E-2</v>
+      </c>
+      <c r="I14" t="str">
         <f t="shared" si="0"/>
+        <v>MCSJK-3N-16.00-3.3-50-B </v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>Supply Current</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
         <v>4.9499999999999995E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>2.6</v>
@@ -1473,13 +1701,21 @@
         <v>0.02</v>
       </c>
       <c r="E15">
+        <f t="shared" si="3"/>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="I15" t="str">
         <f t="shared" si="0"/>
+        <v>HSMS-C170</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1488,44 +1724,55 @@
         <v>0</v>
       </c>
       <c r="E16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>L77HDE15SD1CH4F</v>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="4"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
         <v>0.1066032</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
         <v>2.5199999999999999E-5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1">
         <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
         <v>5.2000000000000005E-2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -1537,7 +1784,7 @@
         <v>0.1586284</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -1546,7 +1793,7 @@
         <v>158.6284</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1565,12 +1812,12 @@
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="18.42578125" customWidth="1"/>
     <col min="14" max="14" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1591,7 +1838,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1602,7 +1849,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1627,9 +1874,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="2">
@@ -1642,10 +1889,23 @@
         <f>(C4*D4)/1000</f>
         <v>0.33</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I4" s="4" t="str">
+        <f>A4</f>
+        <v>TEL0132 </v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4">
+        <f>E4</f>
+        <v>0.33</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="2">
@@ -1658,13 +1918,21 @@
         <f t="shared" ref="E5:E10" si="0">(C5*D5)/1000</f>
         <v>3.9599999999999996E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I5" t="str">
+        <f t="shared" ref="I5:I10" si="1">A5</f>
+        <v>BME680 </v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K10" si="2">E5</f>
+        <v>3.9599999999999996E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>3.3</v>
@@ -1676,10 +1944,22 @@
         <f t="shared" si="0"/>
         <v>0.79200000000000004</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v>MS860702BA01-50</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" ref="J6:J9" si="3">B6</f>
+        <v>25°C, VDD = 3V</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0.79200000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -1691,10 +1971,18 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v>GP2Y1010AU0F</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="16">
@@ -1706,13 +1994,24 @@
         <v>0</v>
       </c>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>SEN0134 </v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2">
         <v>3.3</v>
@@ -1724,10 +2023,25 @@
         <f t="shared" si="0"/>
         <v>1.815E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v>MCP3004-I/SL </v>
+      </c>
+      <c r="J9" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>VDD = VREF = 5V, 
+DOUT unloaded
+VDD = VREF = 2.7V, 
+DOUT unloaded</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>1.815E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2">
         <v>3.3</v>
@@ -1739,52 +2053,60 @@
         <f t="shared" si="0"/>
         <v>2.64</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>XC9141B50DMR-G </v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"3,3")</f>
         <v>3.8034150000000002</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"5,0")</f>
         <v>0.1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"2,6")</f>
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
@@ -1796,7 +2118,7 @@
         <v>3.9034150000000003</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
@@ -1805,7 +2127,7 @@
         <v>3903.4150000000004</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
@@ -1912,10 +2234,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
         <v>3.3</v>
@@ -1928,17 +2250,29 @@
         <f>C4*D4</f>
         <v>2.3099999999999998E-4</v>
       </c>
+      <c r="I4" t="str">
+        <f>A4</f>
+        <v>LAMBDA62-8D</v>
+      </c>
+      <c r="J4" t="str">
+        <f>B4</f>
+        <v>Quiescent current</v>
+      </c>
+      <c r="K4">
+        <f>E4</f>
+        <v>2.3099999999999998E-4</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1">
         <f>E4</f>
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1950,7 +2284,7 @@
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1962,7 +2296,7 @@
         <v>0.23099999999999998</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Invitado(pass user)\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359923FC-000F-4992-B85C-F262156C8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="PCB2.Sensores" sheetId="3" r:id="rId3"/>
     <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="60">
   <si>
     <t>TOTAL</t>
   </si>
@@ -539,13 +540,13 @@
     <t>Theta_jar(Cº/W)</t>
   </si>
   <si>
-    <t>(?)(?)</t>
+    <t>Theta_jar(°C/W)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -616,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -657,6 +658,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,10 +677,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,26 +941,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" customWidth="1"/>
+    <col min="14" max="14" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -973,7 +974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -981,7 +982,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1019,7 +1020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>1.7249999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3"/>
       <c r="G5" s="4"/>
       <c r="J5" s="8" t="s">
@@ -1067,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1103,7 +1104,7 @@
         <v>0.17929999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>5.5799999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1177,11 +1178,9 @@
         <f>K8*M8</f>
         <v>38.015999999999998</v>
       </c>
-      <c r="P8" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="17"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1211,10 +1210,10 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D11" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
@@ -1226,7 +1225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>53</v>
       </c>
@@ -1238,7 +1237,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1264,7 +1263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1276,7 +1275,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D19" s="1">
         <f>D18*1000</f>
         <v>18838.689999999999</v>
@@ -1285,7 +1284,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1297,17 +1296,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1320,7 +1321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1328,7 +1329,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1358,14 +1359,14 @@
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1395,404 +1396,362 @@
         <f>E4</f>
         <v>6.929999999999999E-5</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="N4">
+        <f>K4*M4</f>
+        <v>2.6541899999999994E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
         <f>21*10^(-6)</f>
         <v>2.0999999999999999E-5</v>
       </c>
       <c r="E5">
-        <f>C5*D5</f>
-        <v>6.929999999999999E-5</v>
+        <f t="shared" ref="E5:E13" si="0">C5*D5</f>
+        <v>2.5199999999999999E-5</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I16" si="0">A5</f>
+        <f>A5</f>
         <v>ICE40HX4K-TQ144</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" ref="J5:J14" si="1">B5</f>
-        <v>standby power</v>
+        <f>B5</f>
+        <v xml:space="preserve">power </v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K16" si="2">E5</f>
-        <v>6.929999999999999E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
+        <f>E5</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="M5">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N12" si="1">K5*M5</f>
+        <v>9.6515999999999995E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C6">
         <v>3.3</v>
       </c>
       <c r="D6">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="E6">
-        <f>C6*D6</f>
-        <v>6.929999999999999E-5</v>
+        <f t="shared" si="0"/>
+        <v>3.3000000000000003E-5</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J6" t="str">
+        <f>A6</f>
+        <v>1N4448HSW-7-F </v>
+      </c>
+      <c r="K6">
+        <f>E6</f>
+        <v>3.3000000000000003E-5</v>
+      </c>
+      <c r="M6">
+        <v>222</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="1"/>
-        <v>standby power</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="2"/>
-        <v>6.929999999999999E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
+        <v>7.3260000000000009E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>3.3</v>
       </c>
       <c r="D7">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
-      </c>
-      <c r="E7">
-        <f>C7*D7</f>
-        <v>6.929999999999999E-5</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="1"/>
-        <v>standby power</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="2"/>
-        <v>6.929999999999999E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8">
-        <v>1.2</v>
-      </c>
-      <c r="D8">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ref="E8:E16" si="3">C8*D8</f>
-        <v>2.5199999999999999E-5</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">power </v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
-        <v>2.5199999999999999E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9">
-        <v>3.3</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="0"/>
-        <v>1N4448HSW-7-F </v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10">
-        <v>3.3</v>
-      </c>
-      <c r="D10">
         <f>17*10^(-3)</f>
         <v>1.7000000000000001E-2</v>
       </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="I7" t="str">
+        <f>A7</f>
+        <v>IS25LP032D-JNLE </v>
+      </c>
+      <c r="J7" t="str">
+        <f>B7</f>
+        <v>FRD Quad at 133MHz</v>
+      </c>
+      <c r="K7">
+        <f>E7</f>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>3.3</v>
+      </c>
+      <c r="D8">
+        <f>220*10^(-6)</f>
+        <v>2.1999999999999998E-4</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="I8" s="6" t="str">
+        <f>A8</f>
+        <v>MCP1725-ADJ E/SN </v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f>B8</f>
+        <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
+VOUT = 0.8V to 5.0V</v>
+      </c>
+      <c r="K8">
+        <f>E8</f>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="M8" s="19">
+        <v>163</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>0.11833799999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="str">
+        <f>A9</f>
+        <v>M20-6102045 </v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
       <c r="E10">
-        <f t="shared" si="3"/>
-        <v>5.6100000000000004E-2</v>
-      </c>
-      <c r="I10" t="str">
         <f t="shared" si="0"/>
-        <v>IS25LP032D-JNLE </v>
-      </c>
-      <c r="J10" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="str">
+        <f>A10</f>
+        <v>CON-SIL2</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="N10">
         <f t="shared" si="1"/>
-        <v>FRD Quad at 133MHz</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="2"/>
-        <v>5.6100000000000004E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
       </c>
       <c r="C11">
         <v>3.3</v>
       </c>
       <c r="D11">
-        <f>220*10^(-6)</f>
-        <v>2.1999999999999998E-4</v>
+        <f>15*10^(-3)</f>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E11">
-        <f t="shared" si="3"/>
-        <v>7.2599999999999987E-4</v>
+        <f t="shared" si="0"/>
+        <v>4.9499999999999995E-2</v>
       </c>
       <c r="I11" t="str">
+        <f>A11</f>
+        <v>MCSJK-3N-16.00-3.3-50-B </v>
+      </c>
+      <c r="J11" t="str">
+        <f>B11</f>
+        <v>Supply Current</v>
+      </c>
+      <c r="K11">
+        <f>E11</f>
+        <v>4.9499999999999995E-2</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12">
+        <v>2.6</v>
+      </c>
+      <c r="D12">
+        <f>20*10^(-3)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="0"/>
-        <v>MCP1725-ADJ E/SN </v>
-      </c>
-      <c r="J11" s="7" t="str">
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" t="str">
+        <f>A12</f>
+        <v>HSMS-C170</v>
+      </c>
+      <c r="K12">
+        <f>E12</f>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="M12">
+        <v>400</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
-VOUT = 0.8V to 5.0V</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="2"/>
-        <v>7.2599999999999987E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="str">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <f t="shared" si="0"/>
-        <v>M20-6102045 </v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>CON-SIL2</v>
+        <f>A13</f>
+        <v>L77HDE15SD1CH4F</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4">
-        <f t="shared" si="2"/>
+        <f>E13</f>
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14">
-        <v>3.3</v>
-      </c>
-      <c r="D14">
-        <f>15*10^(-3)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
-        <v>4.9499999999999995E-2</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="0"/>
-        <v>MCSJK-3N-16.00-3.3-50-B </v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="1"/>
-        <v>Supply Current</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="2"/>
-        <v>4.9499999999999995E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>2.6</v>
-      </c>
-      <c r="D15">
-        <f>20*10^(-3)</f>
-        <v>0.02</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
+        <v>0.1064283</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"1,2")</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" si="0"/>
-        <v>HSMS-C170</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>5.2000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>L77HDE15SD1CH4F</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
-        <v>0.1066032</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
-        <v>2.5199999999999999E-5</v>
+        <f>SUM(C16:C18)</f>
+        <v>0.15845350000000002</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C21" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
-        <v>5.2000000000000005E-2</v>
+        <f>C20*1000</f>
+        <v>158.45350000000002</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <f>SUM(C19:C21)</f>
-        <v>0.1586284</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="1">
-        <f>C23*1000</f>
-        <v>158.6284</v>
-      </c>
-      <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1803,21 +1762,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1830,7 +1789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1838,7 +1797,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1874,7 +1833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>21</v>
       </c>
@@ -1903,7 +1862,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>22</v>
       </c>
@@ -1918,7 +1877,7 @@
         <f t="shared" ref="E5:E10" si="0">(C5*D5)/1000</f>
         <v>3.9599999999999996E-2</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I5" s="4" t="str">
         <f t="shared" ref="I5:I10" si="1">A5</f>
         <v>BME680 </v>
       </c>
@@ -1927,7 +1886,7 @@
         <v>3.9599999999999996E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1944,7 +1903,7 @@
         <f t="shared" si="0"/>
         <v>0.79200000000000004</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>MS860702BA01-50</v>
       </c>
@@ -1957,7 +1916,7 @@
         <v>0.79200000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1971,7 +1930,7 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>GP2Y1010AU0F</v>
       </c>
@@ -1980,7 +1939,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
@@ -2006,7 +1965,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -2038,8 +1997,15 @@
         <f t="shared" si="2"/>
         <v>1.815E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>108</v>
+      </c>
+      <c r="N9">
+        <f>K9*M9</f>
+        <v>0.19602</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2062,12 +2028,12 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>45</v>
@@ -2080,7 +2046,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>53</v>
@@ -2093,7 +2059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>52</v>
@@ -2106,10 +2072,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>0</v>
       </c>
@@ -2121,7 +2087,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D18" s="1">
         <f>D17*1000</f>
         <v>3903.4150000000004</v>
@@ -2130,27 +2096,27 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
@@ -2161,21 +2127,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="5" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2188,7 +2154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2196,7 +2162,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2232,7 +2198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2263,7 +2229,7 @@
         <v>2.3099999999999998E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
@@ -2275,7 +2241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2287,7 +2253,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="15"/>
@@ -2299,50 +2265,50 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E18" s="2"/>
     </row>
   </sheetData>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Invitado(pass user)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359923FC-000F-4992-B85C-F262156C8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="PCB2.Sensores" sheetId="3" r:id="rId3"/>
     <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
   <si>
     <t>TOTAL</t>
   </si>
@@ -540,13 +539,13 @@
     <t>Theta_jar(Cº/W)</t>
   </si>
   <si>
-    <t>Theta_jar(°C/W)</t>
+    <t>(?)(?)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -617,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -658,10 +657,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,6 +672,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,26 +940,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" customWidth="1"/>
-    <col min="8" max="8" width="20.109375" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" customWidth="1"/>
-    <col min="10" max="10" width="26.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="18.44140625" customWidth="1"/>
-    <col min="14" max="14" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -974,7 +973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -982,7 +981,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1020,7 +1019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1057,7 +1056,7 @@
         <v>1.7249999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="3"/>
       <c r="G5" s="4"/>
       <c r="J5" s="8" t="s">
@@ -1068,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1104,7 +1103,7 @@
         <v>0.17929999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
@@ -1140,7 +1139,7 @@
         <v>5.5799999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1178,9 +1177,11 @@
         <f>K8*M8</f>
         <v>38.015999999999998</v>
       </c>
-      <c r="P8" s="17"/>
-    </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P8" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1210,10 +1211,10 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>53</v>
       </c>
@@ -1237,7 +1238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1263,7 +1264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <f>D18*1000</f>
         <v>18838.689999999999</v>
@@ -1284,7 +1285,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1296,19 +1297,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
-    <col min="10" max="10" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1321,7 +1320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1329,7 +1328,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1359,14 +1358,14 @@
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1396,362 +1395,404 @@
         <f>E4</f>
         <v>6.929999999999999E-5</v>
       </c>
-      <c r="M4">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="N4">
-        <f>K4*M4</f>
-        <v>2.6541899999999994E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="D5">
         <f>21*10^(-6)</f>
         <v>2.0999999999999999E-5</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E13" si="0">C5*D5</f>
-        <v>2.5199999999999999E-5</v>
+        <f>C5*D5</f>
+        <v>6.929999999999999E-5</v>
       </c>
       <c r="I5" t="str">
-        <f>A5</f>
+        <f t="shared" ref="I5:I16" si="0">A5</f>
         <v>ICE40HX4K-TQ144</v>
       </c>
       <c r="J5" t="str">
-        <f>B5</f>
-        <v xml:space="preserve">power </v>
+        <f t="shared" ref="J5:J14" si="1">B5</f>
+        <v>standby power</v>
       </c>
       <c r="K5">
-        <f>E5</f>
-        <v>2.5199999999999999E-5</v>
-      </c>
-      <c r="M5">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="N5">
-        <f t="shared" ref="N5:N12" si="1">K5*M5</f>
-        <v>9.6515999999999995E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>34</v>
+        <f t="shared" ref="K5:K16" si="2">E5</f>
+        <v>6.929999999999999E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
       </c>
       <c r="C6">
         <v>3.3</v>
       </c>
       <c r="D6">
-        <v>1.0000000000000001E-5</v>
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="E6">
+        <f>C6*D6</f>
+        <v>6.929999999999999E-5</v>
+      </c>
+      <c r="I6" t="str">
         <f t="shared" si="0"/>
-        <v>3.3000000000000003E-5</v>
-      </c>
-      <c r="I6" t="str">
-        <f>A6</f>
-        <v>1N4448HSW-7-F </v>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="1"/>
+        <v>standby power</v>
       </c>
       <c r="K6">
-        <f>E6</f>
-        <v>3.3000000000000003E-5</v>
-      </c>
-      <c r="M6">
-        <v>222</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="1"/>
-        <v>7.3260000000000009E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>6.929999999999999E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>3.3</v>
       </c>
       <c r="D7">
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="E7">
+        <f>C7*D7</f>
+        <v>6.929999999999999E-5</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>standby power</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>6.929999999999999E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>1.2</v>
+      </c>
+      <c r="D8">
+        <f>21*10^(-6)</f>
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ref="E8:E16" si="3">C8*D8</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>ICE40HX4K-TQ144</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">power </v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>2.5199999999999999E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>3.3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>1N4448HSW-7-F </v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>3.3</v>
+      </c>
+      <c r="D10">
         <f>17*10^(-3)</f>
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="E7">
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="I10" t="str">
         <f t="shared" si="0"/>
+        <v>IS25LP032D-JNLE </v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>FRD Quad at 133MHz</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
         <v>5.6100000000000004E-2</v>
       </c>
-      <c r="I7" t="str">
-        <f>A7</f>
-        <v>IS25LP032D-JNLE </v>
-      </c>
-      <c r="J7" t="str">
-        <f>B7</f>
-        <v>FRD Quad at 133MHz</v>
-      </c>
-      <c r="K7">
-        <f>E7</f>
-        <v>5.6100000000000004E-2</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+    </row>
+    <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8">
+      <c r="C11">
         <v>3.3</v>
       </c>
-      <c r="D8">
+      <c r="D11">
         <f>220*10^(-6)</f>
         <v>2.1999999999999998E-4</v>
       </c>
-      <c r="E8">
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="0"/>
-        <v>7.2599999999999987E-4</v>
-      </c>
-      <c r="I8" s="6" t="str">
-        <f>A8</f>
         <v>MCP1725-ADJ E/SN </v>
       </c>
-      <c r="J8" s="7" t="str">
-        <f>B8</f>
+      <c r="J11" s="7" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
 VOUT = 0.8V to 5.0V</v>
       </c>
-      <c r="K8">
-        <f>E8</f>
+      <c r="K11">
+        <f t="shared" si="2"/>
         <v>7.2599999999999987E-4</v>
       </c>
-      <c r="M8" s="19">
-        <v>163</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="1"/>
-        <v>0.11833799999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="str">
-        <f>A9</f>
         <v>M20-6102045 </v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="N9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="str">
-        <f>A10</f>
         <v>CON-SIL2</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="4"/>
-      <c r="N10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>51</v>
       </c>
-      <c r="C11">
+      <c r="C14">
         <v>3.3</v>
       </c>
-      <c r="D11">
+      <c r="D14">
         <f>15*10^(-3)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E11">
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>4.9499999999999995E-2</v>
+      </c>
+      <c r="I14" t="str">
         <f t="shared" si="0"/>
+        <v>MCSJK-3N-16.00-3.3-50-B </v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>Supply Current</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
         <v>4.9499999999999995E-2</v>
       </c>
-      <c r="I11" t="str">
-        <f>A11</f>
-        <v>MCSJK-3N-16.00-3.3-50-B </v>
-      </c>
-      <c r="J11" t="str">
-        <f>B11</f>
-        <v>Supply Current</v>
-      </c>
-      <c r="K11">
-        <f>E11</f>
-        <v>4.9499999999999995E-2</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="C12">
+      <c r="C15">
         <v>2.6</v>
       </c>
-      <c r="D12">
+      <c r="D15">
         <f>20*10^(-3)</f>
         <v>0.02</v>
       </c>
-      <c r="E12">
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="I15" t="str">
         <f t="shared" si="0"/>
+        <v>HSMS-C170</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" t="str">
-        <f>A12</f>
-        <v>HSMS-C170</v>
-      </c>
-      <c r="K12">
-        <f>E12</f>
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="M12">
-        <v>400</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="1"/>
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4" t="str">
-        <f>A13</f>
         <v>L77HDE15SD1CH4F</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4">
-        <f>E13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="1">
-        <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
-        <v>0.1064283</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C19" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
+        <v>0.1066032</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="1">
-        <f>SUMIFS(E$4:E$13,C$4:C$13,"1,2")</f>
+      <c r="C20" s="1">
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
         <v>2.5199999999999999E-5</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="1">
-        <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <f>SUM(C16:C18)</f>
-        <v>0.15845350000000002</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="C21" s="1">
-        <f>C20*1000</f>
-        <v>158.45350000000002</v>
+        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <f>SUM(C19:C21)</f>
+        <v>0.1586284</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="1">
+        <f>C23*1000</f>
+        <v>158.6284</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1762,21 +1803,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
-    <col min="14" max="14" width="17.88671875" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1789,7 +1830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1797,7 +1838,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1833,7 +1874,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>21</v>
       </c>
@@ -1862,7 +1903,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>22</v>
       </c>
@@ -1877,7 +1918,7 @@
         <f t="shared" ref="E5:E10" si="0">(C5*D5)/1000</f>
         <v>3.9599999999999996E-2</v>
       </c>
-      <c r="I5" s="4" t="str">
+      <c r="I5" t="str">
         <f t="shared" ref="I5:I10" si="1">A5</f>
         <v>BME680 </v>
       </c>
@@ -1886,7 +1927,7 @@
         <v>3.9599999999999996E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1903,7 +1944,7 @@
         <f t="shared" si="0"/>
         <v>0.79200000000000004</v>
       </c>
-      <c r="I6" s="4" t="str">
+      <c r="I6" t="str">
         <f t="shared" si="1"/>
         <v>MS860702BA01-50</v>
       </c>
@@ -1916,7 +1957,7 @@
         <v>0.79200000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1930,7 +1971,7 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" t="str">
         <f t="shared" si="1"/>
         <v>GP2Y1010AU0F</v>
       </c>
@@ -1939,7 +1980,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
@@ -1965,7 +2006,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -1997,15 +2038,8 @@
         <f t="shared" si="2"/>
         <v>1.815E-3</v>
       </c>
-      <c r="M9">
-        <v>108</v>
-      </c>
-      <c r="N9">
-        <f>K9*M9</f>
-        <v>0.19602</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2028,12 +2062,12 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>45</v>
@@ -2046,7 +2080,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>53</v>
@@ -2059,7 +2093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>52</v>
@@ -2072,10 +2106,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>0</v>
       </c>
@@ -2087,7 +2121,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <f>D17*1000</f>
         <v>3903.4150000000004</v>
@@ -2096,27 +2130,27 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
@@ -2127,21 +2161,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="5" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2154,7 +2188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2162,7 +2196,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2198,7 +2232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2229,7 +2263,7 @@
         <v>2.3099999999999998E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
@@ -2241,7 +2275,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2253,7 +2287,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="15"/>
@@ -2265,50 +2299,50 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E18" s="2"/>
     </row>
   </sheetData>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId1"/>
-    <sheet name="PCB1.FPGA" sheetId="2" r:id="rId2"/>
-    <sheet name="PCB2.Sensores" sheetId="3" r:id="rId3"/>
-    <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId4"/>
+    <sheet name="TOTAL_V" sheetId="5" r:id="rId1"/>
+    <sheet name="PCB0.Alim_Prog_USB" sheetId="1" r:id="rId2"/>
+    <sheet name="PCB1.FPGA" sheetId="2" r:id="rId3"/>
+    <sheet name="PCB2.Sensores" sheetId="3" r:id="rId4"/>
+    <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="68">
   <si>
     <t>TOTAL</t>
   </si>
@@ -86,9 +87,6 @@
   </si>
   <si>
     <t>LPC1112FD20/102</t>
-  </si>
-  <si>
-    <t>LIPO BAT</t>
   </si>
   <si>
     <t>Currents (µA)</t>
@@ -414,9 +412,6 @@
     <t>M20-6102045 </t>
   </si>
   <si>
-    <t>CON-SIL2</t>
-  </si>
-  <si>
     <t>MCSJK-3N-16.00-3.3-50-B </t>
   </si>
   <si>
@@ -539,7 +534,37 @@
     <t>Theta_jar(Cº/W)</t>
   </si>
   <si>
-    <t>(?)(?)</t>
+    <t>Theta_jar(°C/W)</t>
+  </si>
+  <si>
+    <t>ANALISIS ELECTRICO</t>
+  </si>
+  <si>
+    <t>ANALISIS TÉRMICO</t>
+  </si>
+  <si>
+    <t>ºc</t>
+  </si>
+  <si>
+    <t>t_3,3V</t>
+  </si>
+  <si>
+    <t>t_5V</t>
+  </si>
+  <si>
+    <t>t_2,6V</t>
+  </si>
+  <si>
+    <t>t_3,7V</t>
+  </si>
+  <si>
+    <t>t_1,2V</t>
+  </si>
+  <si>
+    <t>ºC</t>
+  </si>
+  <si>
+    <t>LP735977JH</t>
   </si>
 </sst>
 </file>
@@ -596,12 +621,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -616,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -657,6 +688,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,10 +714,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,6 +979,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C9:H18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12">
+        <f>'PCB0.Alim_Prog_USB'!D15+'PCB1.FPGA'!C16+'PCB2.Sensores'!D13+'PCB3.Antena en PCB'!E6</f>
+        <v>4.2400743000000007</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12">
+        <f>'PCB0.Alim_Prog_USB'!M15+'PCB1.FPGA'!M17+'PCB2.Sensores'!L14+'PCB3.Antena en PCB'!K7</f>
+        <v>38.340338189999997</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13">
+        <f>'PCB0.Alim_Prog_USB'!D14+'PCB2.Sensores'!D14</f>
+        <v>0.10869000000000001</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <f>'PCB0.Alim_Prog_USB'!M14+'PCB1.FPGA'!M16+'PCB2.Sensores'!L13</f>
+        <v>1.9098799999999998</v>
+      </c>
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14">
+        <f>'PCB0.Alim_Prog_USB'!D16+'PCB1.FPGA'!C18+'PCB2.Sensores'!D15</f>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14">
+        <f>'PCB0.Alim_Prog_USB'!M16+'PCB1.FPGA'!M18+'PCB2.Sensores'!L15</f>
+        <v>20.8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15">
+        <f>'PCB0.Alim_Prog_USB'!D17</f>
+        <v>8.879999999999999</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15">
+        <f>'PCB0.Alim_Prog_USB'!M17+'PCB1.FPGA'!M19+'PCB2.Sensores'!L16</f>
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16">
+        <f>'PCB1.FPGA'!C17</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <f>'PCB1.FPGA'!M20+'PCB2.Sensores'!L17</f>
+        <v>9.6515999999999995E-4</v>
+      </c>
+      <c r="H16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <f>SUM(D12:D16)</f>
+        <v>13.280789499999999</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <f>SUM(G12:G16)</f>
+        <v>61.051183349999995</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -992,7 +1185,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1013,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>11</v>
@@ -1024,7 +1217,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3">
         <v>5</v>
@@ -1060,7 +1253,7 @@
       <c r="C5" s="3"/>
       <c r="G5" s="4"/>
       <c r="J5" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N5">
         <f t="shared" ref="N5:N9" si="0">K5*M5</f>
@@ -1072,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -1108,7 +1301,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -1144,7 +1337,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>3.3</v>
@@ -1159,49 +1352,48 @@
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
-      <c r="I8" t="s">
+      <c r="I8" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J8" s="21" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Per supply pin </v>
       </c>
-      <c r="K8">
+      <c r="K8" s="21">
         <f t="shared" si="2"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="M8" s="8">
+      <c r="L8" s="22"/>
+      <c r="M8" s="22">
         <v>115.2</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="21">
         <f>K8*M8</f>
         <v>38.015999999999998</v>
       </c>
-      <c r="P8" s="17" t="s">
-        <v>59</v>
-      </c>
+      <c r="P8" s="17"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2">
         <v>3.7</v>
       </c>
       <c r="D9">
-        <v>5000000</v>
+        <v>2400000</v>
       </c>
       <c r="E9">
         <f>C9*D9*(10^(-6))</f>
-        <v>18.5</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>16</v>
+        <v>8.879999999999999</v>
+      </c>
+      <c r="I9" t="s">
+        <v>67</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4">
         <f t="shared" si="2"/>
-        <v>18.5</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1216,78 +1408,129 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"5")</f>
         <v>8.6899999999999998E-3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" s="1">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"5")</f>
+        <v>1.9098799999999998</v>
+      </c>
+      <c r="N14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="M15" s="1">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"3,3")</f>
+        <v>38.015999999999998</v>
+      </c>
+      <c r="N15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="1">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"2,6")</f>
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1">
-        <v>18.5</v>
+        <f>E9</f>
+        <v>8.879999999999999</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="1">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"3,7")</f>
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D18" s="1">
         <f>SUM(D14:D17)</f>
-        <v>18.83869</v>
+        <v>9.2186899999999987</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <f>SUM(M14:M17)</f>
+        <v>39.925879999999999</v>
+      </c>
+      <c r="N18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <f>D18*1000</f>
-        <v>18838.689999999999</v>
+        <v>9218.6899999999987</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1296,15 +1539,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="23.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1358,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>11</v>
@@ -1367,10 +1612,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>3.3</v>
@@ -1392,249 +1637,288 @@
         <v>standby power</v>
       </c>
       <c r="K4">
-        <f>E4</f>
+        <f t="shared" ref="K4:K13" si="0">E4</f>
         <v>6.929999999999999E-5</v>
+      </c>
+      <c r="M4">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="N4">
+        <f>K4*M4</f>
+        <v>2.6541899999999994E-3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C5">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
         <f>21*10^(-6)</f>
         <v>2.0999999999999999E-5</v>
       </c>
       <c r="E5">
-        <f>C5*D5</f>
-        <v>6.929999999999999E-5</v>
+        <f t="shared" ref="E5:E13" si="1">C5*D5</f>
+        <v>2.5199999999999999E-5</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I16" si="0">A5</f>
+        <f>A5</f>
         <v>ICE40HX4K-TQ144</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" ref="J5:J14" si="1">B5</f>
-        <v>standby power</v>
+        <f>B5</f>
+        <v xml:space="preserve">power </v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K16" si="2">E5</f>
-        <v>6.929999999999999E-5</v>
+        <f t="shared" si="0"/>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="M5">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N12" si="2">K5*M5</f>
+        <v>9.6515999999999995E-4</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="12" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
       </c>
       <c r="C6">
         <v>3.3</v>
       </c>
       <c r="D6">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="E6">
-        <f>C6*D6</f>
-        <v>6.929999999999999E-5</v>
+        <f t="shared" si="1"/>
+        <v>3.3000000000000003E-5</v>
       </c>
       <c r="I6" t="str">
+        <f t="shared" ref="I6:I13" si="3">A6</f>
+        <v>1N4448HSW-7-F </v>
+      </c>
+      <c r="K6">
         <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="1"/>
-        <v>standby power</v>
-      </c>
-      <c r="K6">
+        <v>3.3000000000000003E-5</v>
+      </c>
+      <c r="M6">
+        <v>222</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="2"/>
-        <v>6.929999999999999E-5</v>
+        <v>7.3260000000000009E-3</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
+      <c r="A7" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>3.3</v>
       </c>
       <c r="D7">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
-      </c>
-      <c r="E7">
-        <f>C7*D7</f>
-        <v>6.929999999999999E-5</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="1"/>
-        <v>standby power</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="2"/>
-        <v>6.929999999999999E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8">
-        <v>1.2</v>
-      </c>
-      <c r="D8">
-        <f>21*10^(-6)</f>
-        <v>2.0999999999999999E-5</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ref="E8:E16" si="3">C8*D8</f>
-        <v>2.5199999999999999E-5</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="0"/>
-        <v>ICE40HX4K-TQ144</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">power </v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
-        <v>2.5199999999999999E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9">
-        <v>3.3</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="0"/>
-        <v>1N4448HSW-7-F </v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10">
-        <v>3.3</v>
-      </c>
-      <c r="D10">
         <f>17*10^(-3)</f>
         <v>1.7000000000000001E-2</v>
       </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="3"/>
+        <v>IS25LP032D-JNLE </v>
+      </c>
+      <c r="J7" t="str">
+        <f>B7</f>
+        <v>FRD Quad at 133MHz</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>5.6100000000000004E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>3.3</v>
+      </c>
+      <c r="D8">
+        <f>220*10^(-6)</f>
+        <v>2.1999999999999998E-4</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="I8" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>MCP1725-ADJ E/SN </v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f>B8</f>
+        <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
+VOUT = 0.8V to 5.0V</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>7.2599999999999987E-4</v>
+      </c>
+      <c r="M8" s="19">
+        <v>163</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="2"/>
+        <v>0.11833799999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>M20-6102045 </v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="N9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>109296002381906</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
       <c r="E10">
-        <f t="shared" si="3"/>
-        <v>5.6100000000000004E-2</v>
-      </c>
-      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="20">
+        <v>109296002381906</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4">
         <f t="shared" si="0"/>
-        <v>IS25LP032D-JNLE </v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="1"/>
-        <v>FRD Quad at 133MHz</v>
-      </c>
-      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="N10">
         <f t="shared" si="2"/>
-        <v>5.6100000000000004E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
       </c>
       <c r="C11">
         <v>3.3</v>
       </c>
       <c r="D11">
-        <f>220*10^(-6)</f>
-        <v>2.1999999999999998E-4</v>
+        <f>15*10^(-3)</f>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E11">
+        <f t="shared" si="1"/>
+        <v>4.9499999999999995E-2</v>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="3"/>
-        <v>7.2599999999999987E-4</v>
-      </c>
-      <c r="I11" t="str">
+        <v>MCSJK-3N-16.00-3.3-50-B </v>
+      </c>
+      <c r="J11" t="str">
+        <f>B11</f>
+        <v>Supply Current</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="0"/>
-        <v>MCP1725-ADJ E/SN </v>
-      </c>
-      <c r="J11" s="7" t="str">
+        <v>4.9499999999999995E-2</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>2.6</v>
+      </c>
+      <c r="D12">
+        <f>20*10^(-3)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> IL = 0 mA, VIN = Note 1,
-VOUT = 0.8V to 5.0V</v>
-      </c>
-      <c r="K11">
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>HSMS-C170</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21">
+        <f t="shared" si="0"/>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21">
+        <v>400</v>
+      </c>
+      <c r="N12" s="21">
         <f t="shared" si="2"/>
-        <v>7.2599999999999987E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>M20-6102045 </v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="4"/>
+        <v>20.8</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>38</v>
+      <c r="A13" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1643,157 +1927,141 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>CON-SIL2</v>
+        <f t="shared" si="3"/>
+        <v>L77HDE15SD1CH4F</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
+        <v>0.1064283</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="L16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14">
-        <v>3.3</v>
-      </c>
-      <c r="D14">
-        <f>15*10^(-3)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
-        <v>4.9499999999999995E-2</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="0"/>
-        <v>MCSJK-3N-16.00-3.3-50-B </v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="1"/>
-        <v>Supply Current</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="2"/>
-        <v>4.9499999999999995E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>2.6</v>
-      </c>
-      <c r="D15">
-        <f>20*10^(-3)</f>
-        <v>0.02</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
+      <c r="M16">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"5")</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"1,2")</f>
+        <v>2.5199999999999999E-5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M17">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"3,3")</f>
+        <v>0.12831819</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1">
+        <f>SUMIFS(E$4:E$13,C$4:C$13,"2,6")</f>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" si="0"/>
-        <v>HSMS-C170</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>5.2000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="D18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>L77HDE15SD1CH4F</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="L18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"2,6")</f>
+        <v>20.8</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"3,7")</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <f>SUM(C16:C18)</f>
+        <v>0.15845350000000002</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M20">
+        <f>SUMIFS(N$4:N$13,C$4:C$13,"1,2")</f>
+        <v>9.6515999999999995E-4</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C21" s="1">
+        <f>C20*1000</f>
+        <v>158.45350000000002</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"3,3")</f>
-        <v>0.1066032</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"1,2")</f>
-        <v>2.5199999999999999E-5</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="1">
-        <f>SUMIFS(E$4:E$16,C$4:C$16,"2,6")</f>
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <f>SUM(C19:C21)</f>
-        <v>0.1586284</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="1">
-        <f>C23*1000</f>
-        <v>158.6284</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>47</v>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <f>SUM(M16:M20)</f>
+        <v>20.929283350000002</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +2070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1849,7 +2117,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1876,7 +2144,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="2">
@@ -1905,7 +2173,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="2">
@@ -1918,7 +2186,7 @@
         <f t="shared" ref="E5:E10" si="0">(C5*D5)/1000</f>
         <v>3.9599999999999996E-2</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I5" s="4" t="str">
         <f t="shared" ref="I5:I10" si="1">A5</f>
         <v>BME680 </v>
       </c>
@@ -1929,10 +2197,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>3.3</v>
@@ -1944,7 +2212,7 @@
         <f t="shared" si="0"/>
         <v>0.79200000000000004</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>MS860702BA01-50</v>
       </c>
@@ -1959,7 +2227,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -1971,7 +2239,7 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>GP2Y1010AU0F</v>
       </c>
@@ -1982,7 +2250,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="16">
@@ -2008,10 +2276,10 @@
     </row>
     <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2">
         <v>3.3</v>
@@ -2038,10 +2306,17 @@
         <f t="shared" si="2"/>
         <v>1.815E-3</v>
       </c>
+      <c r="M9">
+        <v>108</v>
+      </c>
+      <c r="N9">
+        <f>K9*M9</f>
+        <v>0.19602</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2">
         <v>3.3</v>
@@ -2053,7 +2328,7 @@
         <f t="shared" si="0"/>
         <v>2.64</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I10" s="4" t="str">
         <f t="shared" si="1"/>
         <v>XC9141B50DMR-G </v>
       </c>
@@ -2070,46 +2345,86 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"3,3")</f>
         <v>3.8034150000000002</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13">
+        <f>SUMIFS(N$4:N$11,C$4:C$11,"5")</f>
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"5,0")</f>
         <v>0.1</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="L14">
+        <f>SUMIFS(N$4:N$11,C$4:C$11,"3,3")</f>
+        <v>0.19602</v>
+      </c>
+      <c r="M14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"2,6")</f>
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15">
+        <f>SUMIFS(N$4:N$11,C$4:C$11,"2,6")</f>
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="K16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16">
+        <f>SUMIFS(N$4:N$11,C$4:C$11,"3,7")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>0</v>
       </c>
@@ -2118,39 +2433,59 @@
         <v>3.9034150000000003</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17">
+        <f>SUMIFS(N$4:N$11,C$4:C$11,"1,2")</f>
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <f>D17*1000</f>
         <v>3903.4150000000004</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="K20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f>SUM(L13:L17)</f>
+        <v>0.19602</v>
+      </c>
+      <c r="M20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
@@ -2160,7 +2495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2207,7 +2542,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -2234,10 +2569,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3">
         <v>3.3</v>
@@ -2265,15 +2600,16 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1">
         <f>E4</f>
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
@@ -2284,7 +2620,17 @@
         <v>2.3099999999999998E-4</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="K7">
+        <f>N4</f>
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2296,7 +2642,17 @@
         <v>0.23099999999999998</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f>K7</f>
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -2304,12 +2660,14 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="4"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL_V" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="67">
   <si>
     <t>TOTAL</t>
   </si>
@@ -562,9 +562,6 @@
   </si>
   <si>
     <t>ºC</t>
-  </si>
-  <si>
-    <t>LP735977JH</t>
   </si>
 </sst>
 </file>
@@ -647,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -696,8 +693,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="D12">
         <f>'PCB0.Alim_Prog_USB'!D15+'PCB1.FPGA'!C16+'PCB2.Sensores'!D13+'PCB3.Antena en PCB'!E6</f>
-        <v>4.2400743000000007</v>
+        <v>4.7699743000000003</v>
       </c>
       <c r="E12" t="s">
         <v>41</v>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="G12">
         <f>'PCB0.Alim_Prog_USB'!M15+'PCB1.FPGA'!M17+'PCB2.Sensores'!L14+'PCB3.Antena en PCB'!K7</f>
-        <v>38.340338189999997</v>
+        <v>140.01481819</v>
       </c>
       <c r="H12" t="s">
         <v>60</v>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="D13">
         <f>'PCB0.Alim_Prog_USB'!D14+'PCB2.Sensores'!D14</f>
-        <v>0.10869000000000001</v>
+        <v>0.10759000000000001</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
@@ -1032,7 +1036,7 @@
       </c>
       <c r="G13">
         <f>'PCB0.Alim_Prog_USB'!M14+'PCB1.FPGA'!M16+'PCB2.Sensores'!L13</f>
-        <v>1.9098799999999998</v>
+        <v>1.7305799999999998</v>
       </c>
       <c r="H13" t="s">
         <v>60</v>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="G14">
         <f>'PCB0.Alim_Prog_USB'!M16+'PCB1.FPGA'!M18+'PCB2.Sensores'!L15</f>
-        <v>20.8</v>
+        <v>13.000000000000002</v>
       </c>
       <c r="H14" t="s">
         <v>60</v>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="D15">
         <f>'PCB0.Alim_Prog_USB'!D17</f>
-        <v>8.879999999999999</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
         <v>41</v>
@@ -1110,7 +1114,7 @@
       </c>
       <c r="D18" s="1">
         <f>SUM(D12:D16)</f>
-        <v>13.280789499999999</v>
+        <v>4.9295894999999996</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>41</v>
@@ -1120,7 +1124,7 @@
       </c>
       <c r="G18" s="1">
         <f>SUM(G12:G16)</f>
-        <v>61.051183349999995</v>
+        <v>154.74636335</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>60</v>
@@ -1268,32 +1272,33 @@
         <v>18</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D6">
-        <v>220</v>
+        <v>5000</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E7" si="1">C6*D6*(10^(-6))</f>
-        <v>1.0999999999999998E-3</v>
-      </c>
-      <c r="I6" s="6" t="s">
+        <f>(5-3.3)*(500000)/10^6</f>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="7" t="str">
+      <c r="J6" s="25" t="str">
         <f>B6</f>
         <v xml:space="preserve">IL = 0 mA, VIN = Note 1             VOUT = 0.8V to 5.0V </v>
       </c>
-      <c r="K6">
-        <f t="shared" ref="K6:K9" si="2">E6</f>
-        <v>1.0999999999999998E-3</v>
-      </c>
-      <c r="M6">
+      <c r="K6" s="21">
+        <f t="shared" ref="K6:K9" si="1">E6</f>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21">
         <v>163</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="21">
         <f t="shared" si="0"/>
-        <v>0.17929999999999999</v>
+        <v>138.55000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1310,7 +1315,7 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E6:E7" si="2">C7*D7*(10^(-6))</f>
         <v>8.9999999999999992E-5</v>
       </c>
       <c r="I7" s="10" t="s">
@@ -1321,7 +1326,7 @@
         <v>USB 2.0 FS, UART at 1-Mbps single channel, no GPIO switching at VCC = 5 V,       VCCIO = 5 V</v>
       </c>
       <c r="K7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8.9999999999999992E-5</v>
       </c>
       <c r="M7">
@@ -1343,64 +1348,43 @@
         <v>3.3</v>
       </c>
       <c r="D8" s="2">
-        <v>100000</v>
+        <v>3000</v>
       </c>
       <c r="E8">
         <f>C8*D8*(10^(-6))</f>
-        <v>0.32999999999999996</v>
+        <v>9.8999999999999991E-3</v>
       </c>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="21" t="str">
+      <c r="J8" s="22" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Per supply pin </v>
       </c>
-      <c r="K8" s="21">
-        <f t="shared" si="2"/>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22">
+      <c r="K8" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8999999999999991E-3</v>
+      </c>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23">
         <v>115.2</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="22">
         <f>K8*M8</f>
-        <v>38.015999999999998</v>
+        <v>1.1404799999999999</v>
       </c>
       <c r="P8" s="17"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="D9">
-        <v>2400000</v>
-      </c>
-      <c r="E9">
-        <f>C9*D9*(10^(-6))</f>
-        <v>8.879999999999999</v>
-      </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4">
-        <f t="shared" si="2"/>
-        <v>8.879999999999999</v>
-      </c>
+      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1412,7 +1396,7 @@
       </c>
       <c r="D14" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"5")</f>
-        <v>8.6899999999999998E-3</v>
+        <v>7.5899999999999995E-3</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>41</v>
@@ -1422,7 +1406,7 @@
       </c>
       <c r="M14" s="1">
         <f>SUMIFS(N$4:N$13,C$4:C$13,"5")</f>
-        <v>1.9098799999999998</v>
+        <v>1.7305799999999998</v>
       </c>
       <c r="N14" t="s">
         <v>60</v>
@@ -1434,7 +1418,7 @@
       </c>
       <c r="D15" s="1">
         <f>SUMIFS(E$4:E$13,C$4:C$13,"3,3")</f>
-        <v>0.32999999999999996</v>
+        <v>0.85990000000000011</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>41</v>
@@ -1444,7 +1428,7 @@
       </c>
       <c r="M15" s="1">
         <f>SUMIFS(N$4:N$13,C$4:C$13,"3,3")</f>
-        <v>38.015999999999998</v>
+        <v>139.69048000000001</v>
       </c>
       <c r="N15" t="s">
         <v>60</v>
@@ -1481,7 +1465,7 @@
       </c>
       <c r="D17" s="1">
         <f>E9</f>
-        <v>8.879999999999999</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>41</v>
@@ -1503,7 +1487,7 @@
       </c>
       <c r="D18" s="1">
         <f>SUM(D14:D17)</f>
-        <v>9.2186899999999987</v>
+        <v>0.86749000000000009</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>41</v>
@@ -1513,7 +1497,7 @@
       </c>
       <c r="M18" s="1">
         <f>SUM(M14:M17)</f>
-        <v>39.925879999999999</v>
+        <v>141.42106000000001</v>
       </c>
       <c r="N18" t="s">
         <v>60</v>
@@ -1522,7 +1506,7 @@
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <f>D18*1000</f>
-        <v>9218.6899999999987</v>
+        <v>867.49000000000012</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>45</v>
@@ -1898,22 +1882,22 @@
         <v>5.2000000000000005E-2</v>
       </c>
       <c r="H12" s="4"/>
-      <c r="I12" s="21" t="str">
+      <c r="I12" s="22" t="str">
         <f t="shared" si="3"/>
         <v>HSMS-C170</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21">
+      <c r="J12" s="22"/>
+      <c r="K12" s="22">
         <f t="shared" si="0"/>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21">
-        <v>400</v>
-      </c>
-      <c r="N12" s="21">
+      <c r="L12" s="22"/>
+      <c r="M12" s="22">
+        <v>250</v>
+      </c>
+      <c r="N12" s="22">
         <f t="shared" si="2"/>
-        <v>20.8</v>
+        <v>13.000000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2003,7 +1987,7 @@
       </c>
       <c r="M18">
         <f>SUMIFS(N$4:N$13,C$4:C$13,"2,6")</f>
-        <v>20.8</v>
+        <v>13.000000000000002</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>66</v>
@@ -2058,7 +2042,7 @@
       </c>
       <c r="M23" s="1">
         <f>SUM(M16:M20)</f>
-        <v>20.929283350000002</v>
+        <v>13.129283350000001</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>66</v>

--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico-C.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Invitado(pass user)\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Hardware/Analisis Eléctrico y Térmico/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_18729C5ECA509F0E2D7D153F4F321D47E9C7C5C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B821B225-A2F2-45AB-8754-6795054D5DDD}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL_V" sheetId="5" r:id="rId1"/>
@@ -18,7 +19,7 @@
     <sheet name="PCB2.Sensores" sheetId="3" r:id="rId4"/>
     <sheet name="PCB3.Antena en PCB" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="68">
   <si>
     <t>TOTAL</t>
   </si>
@@ -562,12 +563,15 @@
   </si>
   <si>
     <t>ºC</t>
+  </si>
+  <si>
+    <t>temperature increase over humidity sensor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -644,7 +648,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -688,15 +692,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -982,7 +981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C9:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1004,7 +1003,7 @@
       </c>
       <c r="D12">
         <f>'PCB0.Alim_Prog_USB'!D15+'PCB1.FPGA'!C16+'PCB2.Sensores'!D13+'PCB3.Antena en PCB'!E6</f>
-        <v>4.7699743000000003</v>
+        <v>4.5224743000000007</v>
       </c>
       <c r="E12" t="s">
         <v>41</v>
@@ -1014,7 +1013,7 @@
       </c>
       <c r="G12">
         <f>'PCB0.Alim_Prog_USB'!M15+'PCB1.FPGA'!M17+'PCB2.Sensores'!L14+'PCB3.Antena en PCB'!K7</f>
-        <v>140.01481819</v>
+        <v>141.51481819</v>
       </c>
       <c r="H12" t="s">
         <v>60</v>
@@ -1114,7 +1113,7 @@
       </c>
       <c r="D18" s="1">
         <f>SUM(D12:D16)</f>
-        <v>4.9295894999999996</v>
+        <v>4.6820895</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>41</v>
@@ -1124,7 +1123,7 @@
       </c>
       <c r="G18" s="1">
         <f>SUM(G12:G16)</f>
-        <v>154.74636335</v>
+        <v>156.24636335</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>60</v>
@@ -1137,7 +1136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1260,7 +1259,7 @@
         <v>55</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:N9" si="0">K5*M5</f>
+        <f t="shared" ref="N5:N7" si="0">K5*M5</f>
         <v>0</v>
       </c>
     </row>
@@ -1281,22 +1280,22 @@
         <f>(5-3.3)*(500000)/10^6</f>
         <v>0.85000000000000009</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="25" t="str">
+      <c r="J6" s="22" t="str">
         <f>B6</f>
         <v xml:space="preserve">IL = 0 mA, VIN = Note 1             VOUT = 0.8V to 5.0V </v>
       </c>
-      <c r="K6" s="21">
-        <f t="shared" ref="K6:K9" si="1">E6</f>
+      <c r="K6" s="20">
+        <f t="shared" ref="K6:K8" si="1">E6</f>
         <v>0.85000000000000009</v>
       </c>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21">
+      <c r="L6" s="20"/>
+      <c r="M6" s="20">
         <v>163</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="20">
         <f t="shared" si="0"/>
         <v>138.55000000000001</v>
       </c>
@@ -1315,7 +1314,7 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <f t="shared" ref="E6:E7" si="2">C7*D7*(10^(-6))</f>
+        <f t="shared" ref="E7" si="2">C7*D7*(10^(-6))</f>
         <v>8.9999999999999992E-5</v>
       </c>
       <c r="I7" s="10" t="s">
@@ -1357,22 +1356,21 @@
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
-      <c r="I8" s="22" t="s">
+      <c r="I8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="22" t="str">
+      <c r="J8" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Per supply pin </v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8">
         <f t="shared" si="1"/>
         <v>9.8999999999999991E-3</v>
       </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="M8" s="8">
         <v>115.2</v>
       </c>
-      <c r="N8" s="22">
+      <c r="N8">
         <f>K8*M8</f>
         <v>1.1404799999999999</v>
       </c>
@@ -1524,7 +1522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1766,7 +1764,7 @@
         <f t="shared" si="0"/>
         <v>7.2599999999999987E-4</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8">
         <v>163</v>
       </c>
       <c r="N8">
@@ -1804,7 +1802,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>109296002381906</v>
       </c>
       <c r="C10">
@@ -1817,7 +1815,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="19">
         <v>109296002381906</v>
       </c>
       <c r="J10" s="4"/>
@@ -1882,20 +1880,18 @@
         <v>5.2000000000000005E-2</v>
       </c>
       <c r="H12" s="4"/>
-      <c r="I12" s="22" t="str">
+      <c r="I12" t="str">
         <f t="shared" si="3"/>
         <v>HSMS-C170</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22">
+      <c r="K12">
         <f t="shared" si="0"/>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22">
+      <c r="M12">
         <v>250</v>
       </c>
-      <c r="N12" s="22">
+      <c r="N12">
         <f t="shared" si="2"/>
         <v>13.000000000000002</v>
       </c>
@@ -2055,14 +2051,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="18.42578125" customWidth="1"/>
@@ -2135,11 +2131,11 @@
         <v>3.3</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <f>(C4*D4)/1000</f>
-        <v>0.33</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="I4" s="4" t="str">
         <f>A4</f>
@@ -2148,7 +2144,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4">
         <f>E4</f>
-        <v>0.33</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -2207,6 +2203,12 @@
       <c r="K6">
         <f t="shared" si="2"/>
         <v>0.79200000000000004</v>
+      </c>
+      <c r="N6">
+        <v>1.5</v>
+      </c>
+      <c r="O6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -2333,7 +2335,7 @@
       </c>
       <c r="D13" s="1">
         <f>SUMIFS(E$4:E$11,C$4:C$11,"3,3")</f>
-        <v>3.8034150000000002</v>
+        <v>3.5559150000000002</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>41</v>
@@ -2366,7 +2368,7 @@
       </c>
       <c r="L14">
         <f>SUMIFS(N$4:N$11,C$4:C$11,"3,3")</f>
-        <v>0.19602</v>
+        <v>1.6960200000000001</v>
       </c>
       <c r="M14" t="s">
         <v>60</v>
@@ -2414,7 +2416,7 @@
       </c>
       <c r="D17" s="1">
         <f>SUM(D13:D15)</f>
-        <v>3.9034150000000003</v>
+        <v>3.6559150000000002</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>41</v>
@@ -2433,7 +2435,7 @@
     <row r="18" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <f>D17*1000</f>
-        <v>3903.4150000000004</v>
+        <v>3655.9150000000004</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>45</v>
@@ -2453,7 +2455,7 @@
       </c>
       <c r="L20">
         <f>SUM(L13:L17)</f>
-        <v>0.19602</v>
+        <v>1.6960200000000001</v>
       </c>
       <c r="M20" t="s">
         <v>60</v>
@@ -2480,7 +2482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
